--- a/output/draft-cheat-sheet.xlsx
+++ b/output/draft-cheat-sheet.xlsx
@@ -651,6 +651,7 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -966,7 +967,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>When a source leaves a player off entirely, that counts as a rank just past the end of their list rather than being ignored — being omitted from a 300-player board is information.</t>
+          <t>When a source leaves a player off entirely, that counts as a rank just past the end of their list rather than being ignored — being omitted from a board is information. These update from the actual list sizes on every rebuild.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>capped at top 300</t>
+          <t>list is 300 deep</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1057,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>capped at top 300</t>
+          <t>list is 300 deep</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Filter with the header arrows. Set Drafted to dim a row. A shaded Range means the sources disagree by 42 or more.</t>
+          <t>Filter with the header arrows. Set Drafted to dim a row. A shaded Range means the sources disagree by 40 or more.</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16749,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L331">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="2">
-      <formula>42</formula>
+      <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -16795,7 +16796,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Filter with the header arrows. Set Drafted to dim a row. A shaded Range means the sources disagree by 42 or more.</t>
+          <t>Filter with the header arrows. Set Drafted to dim a row. A shaded Range means the sources disagree by 40 or more.</t>
         </is>
       </c>
     </row>
@@ -32675,7 +32676,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L337">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="2">
-      <formula>42</formula>
+      <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
